--- a/artfynd/A 69056-2020 artfynd.xlsx
+++ b/artfynd/A 69056-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 69056-2020 artfynd.xlsx
+++ b/artfynd/A 69056-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY80"/>
+  <dimension ref="A1:AY81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10031,6 +10031,133 @@
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>105333967</v>
+      </c>
+      <c r="B81" t="n">
+        <v>56435</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>100045</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Sångsvan</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Cygnus cygnus</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>sträckande SV</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Murmossen, Ramnäs, Vstm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>560539</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6627590</v>
+      </c>
+      <c r="S81" t="n">
+        <v>50</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2022-12-24</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2022-12-24</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Plog som kom från öster norr om Salsmossen och flög SV mot Stenramenhållet</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 69056-2020 artfynd.xlsx
+++ b/artfynd/A 69056-2020 artfynd.xlsx
@@ -10036,7 +10036,7 @@
         <v>105333967</v>
       </c>
       <c r="B81" t="n">
-        <v>56435</v>
+        <v>56529</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
